--- a/cosmos-graph/reports/Instrument_Category_Resolution.xlsx
+++ b/cosmos-graph/reports/Instrument_Category_Resolution.xlsx
@@ -469,7 +469,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-12 21:25</t>
+          <t>Generated: 2026-08-23 19:04</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -795,51 +795,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>APACHE II</t>
+          <t>AJCC Cancer Staging Manual 7th Edition Clinical Classification</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>synonym</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>C121005</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Acute Physiology and Chronic Health Evaluation II Clinical Classification</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>APACHE II Clinical Classification Question</t>
+          <t>AJCC V7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C120994</t>
+          <t>C125755</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>APACHE II Clinical Classification Question</t>
+          <t>AJCC Cancer Staging Manual 7th Edition</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>APCH1</t>
+          <t>AJCC V7 Clinical Classification Question</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -853,7 +845,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ATLAS</t>
+          <t>APACHE II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -863,19 +855,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C147589</t>
+          <t>C121005</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ATLAS Score Clinical Classification</t>
+          <t>Acute Physiology and Chronic Health Evaluation II Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ATLAS Clinical Classification Question</t>
+          <t>APACHE II Clinical Classification Question</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -885,41 +877,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C147551</t>
+          <t>C120994</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ATLAS Clinical Classification Question</t>
+          <t>APACHE II Clinical Classification Question</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ATLAS Score Clinical Classification</t>
+          <t>APCH1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>exact_name</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>C147589</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ATLAS Score Clinical Classification</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ATLAS1</t>
+          <t>ATLAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -941,7 +925,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abnormal Involuntary Movement Scale Clinical Classification</t>
+          <t>ATLAS Clinical Classification Question</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -951,55 +935,63 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C102111</t>
+          <t>C147551</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Abnormal Involuntary Movement Scale Clinical Classification</t>
+          <t>ATLAS Clinical Classification Question</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Acceptability Surveys</t>
+          <t>ATLAS Score Clinical Classification</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>exact_name</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>C147589</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ATLAS Score Clinical Classification</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Acute Physiology and Chronic Health Evaluation II Clinical Classification</t>
+          <t>ATLAS1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C121005</t>
+          <t>C147589</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Acute Physiology and Chronic Health Evaluation II Clinical Classification</t>
+          <t>ATLAS Score Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alzheimer's Disease Assessment Scale-Cognitive CDISC Version Functional Test</t>
+          <t>Abnormal Involuntary Movement Scale Clinical Classification</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1009,41 +1001,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C100762</t>
+          <t>C102111</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Alzheimer's Disease Assessment Scale-Cognitive CDISC Version Functional Test</t>
+          <t>Abnormal Involuntary Movement Scale Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BPRS-A</t>
+          <t>Acceptability Surveys</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>synonym</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>C100761</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Brief Psychiatric Rating Scale A Clinical Classification</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BPRS-Anchored Clinical Classification Question</t>
+          <t>Acute Physiology and Chronic Health Evaluation II Clinical Classification</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1053,46 +1037,46 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>C100109</t>
+          <t>C121005</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BPRS-Anchored Clinical Classification Question</t>
+          <t>Acute Physiology and Chronic Health Evaluation II Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BPRSA1</t>
+          <t>Alzheimer's Disease Assessment Scale-Cognitive CDISC Version Functional Test</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>exact_name</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>C100761</t>
+          <t>C100762</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Brief Psychiatric Rating Scale A Clinical Classification</t>
+          <t>Alzheimer's Disease Assessment Scale-Cognitive CDISC Version Functional Test</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brief Psychiatric Rating Scale A Clinical Classification</t>
+          <t>BPRS-A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1109,73 +1093,73 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CES</t>
+          <t>BPRS-Anchored Clinical Classification Question</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>exact_name</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>C132532</t>
+          <t>C100109</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Combat Exposure Scale Questionnaire</t>
+          <t>BPRS-Anchored Clinical Classification Question</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CES Questionnaire Question</t>
+          <t>BPRSA1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>C132527</t>
+          <t>C100761</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CES Questionnaire Question</t>
+          <t>Brief Psychiatric Rating Scale A Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CES01</t>
+          <t>Brief Psychiatric Rating Scale A Clinical Classification</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>exact_name</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>C132532</t>
+          <t>C100761</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Combat Exposure Scale Questionnaire</t>
+          <t>Brief Psychiatric Rating Scale A Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CHILD-PUGH CLASSIFICATION</t>
+          <t>CES</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1185,41 +1169,41 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>C121007</t>
+          <t>C132532</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Child-Pugh Clinical Classification</t>
+          <t>Combat Exposure Scale Questionnaire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CPS01</t>
+          <t>CES Questionnaire Question</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>exact_name</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>C121007</t>
+          <t>C132527</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Child-Pugh Clinical Classification</t>
+          <t>CES Questionnaire Question</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Child-Pugh</t>
+          <t>CES01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1229,24 +1213,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>C121007</t>
+          <t>C132532</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Child-Pugh Clinical Classification</t>
+          <t>Combat Exposure Scale Questionnaire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Child-Pugh Clinical Classification</t>
+          <t>CHILD-PUGH CLASSIFICATION</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1263,51 +1247,51 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Child-Pugh Clinical Classification Question</t>
+          <t>CPS01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>C120996</t>
+          <t>C121007</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Child-Pugh Clinical Classification Question</t>
+          <t>Child-Pugh Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Classification</t>
+          <t>Child-Pugh</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>C118969</t>
+          <t>C121007</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Classification</t>
+          <t>Child-Pugh Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Questionnaire</t>
+          <t>Child-Pugh Clinical Classification</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1317,19 +1301,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>C91105</t>
+          <t>C121007</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Questionnaire</t>
+          <t>Child-Pugh Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Combat Exposure Scale Questionnaire</t>
+          <t>Child-Pugh Clinical Classification Question</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1339,19 +1323,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>C132532</t>
+          <t>C120996</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Combat Exposure Scale Questionnaire</t>
+          <t>Child-Pugh Clinical Classification Question</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Clinical or Research Assessment Classification</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1361,91 +1345,99 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>C50995</t>
+          <t>C118969</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Disease Response</t>
+          <t>Clinical or Research Assessment Classification</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Disease Response Criteria</t>
+          <t>Clinical or Research Assessment Questionnaire</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+          <t>exact_name</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>C91105</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Questionnaire</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Disease Response and Clinical Classification</t>
+          <t>Combat Exposure Scale Questionnaire</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+          <t>exact_name</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>C132532</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Combat Exposure Scale Questionnaire</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ECOG</t>
+          <t>Disease Response</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>exact_name</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>C102116</t>
+          <t>C50995</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Eastern Cooperative Oncology Group Performance Status Clinical Classification</t>
+          <t>Disease Response</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ECOG Clinical Classification Question</t>
+          <t>Disease Response Criteria</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>exact_name</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>C101874</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>ECOG Clinical Classification Question</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ECOG1</t>
+          <t>Disease Response and Clinical Classification</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1459,7 +1451,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EQ-5D-5L</t>
+          <t>ECOG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1469,19 +1461,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>C102117</t>
+          <t>C102116</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>European Quality of Life Five Dimension Five Level Scale Questionnaire</t>
+          <t>Eastern Cooperative Oncology Group Performance Status Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EQ-5D-5L Questionnaire Question</t>
+          <t>ECOG Clinical Classification Question</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1491,63 +1483,55 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>C101875</t>
+          <t>C101874</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EQ-5D-5L Questionnaire Question</t>
+          <t>ECOG Clinical Classification Question</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EQ5D02</t>
+          <t>ECOG1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>synonym</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>C102117</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>European Quality of Life Five Dimension Five Level Scale Questionnaire</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Eastern Cooperative Oncology Group Performance Status Clinical Classification</t>
+          <t>EQ-5D-5L</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>C102116</t>
+          <t>C102117</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Eastern Cooperative Oncology Group Performance Status Clinical Classification</t>
+          <t>European Quality of Life Five Dimension Five Level Scale Questionnaire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>European Quality of Life Five Dimension Five Level Scale Questionnaire</t>
+          <t>EQ-5D-5L Questionnaire Question</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1557,85 +1541,85 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>C102117</t>
+          <t>C101875</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>European Quality of Life Five Dimension Five Level Scale Questionnaire</t>
+          <t>EQ-5D-5L Questionnaire Question</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Functional Assessment</t>
+          <t>EQ5D02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>C81250</t>
+          <t>C102117</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Functional Assessment</t>
+          <t>European Quality of Life Five Dimension Five Level Scale Questionnaire</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HAM-A</t>
+          <t>Eastern Cooperative Oncology Group Performance Status Clinical Classification</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>exact_name</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>C102118</t>
+          <t>C102116</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Hamilton Anxiety Rating Scale Clinical Classification</t>
+          <t>Eastern Cooperative Oncology Group Performance Status Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HAMA</t>
+          <t>European Quality of Life Five Dimension Five Level Scale Questionnaire</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>exact_name</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>C102118</t>
+          <t>C102117</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Hamilton Anxiety Rating Scale Clinical Classification</t>
+          <t>European Quality of Life Five Dimension Five Level Scale Questionnaire</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HAMA Questionnaire Question</t>
+          <t>Functional Assessment</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1645,19 +1629,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>C101876</t>
+          <t>C81250</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>HAMA Questionnaire Question</t>
+          <t>Functional Assessment</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HAMA1</t>
+          <t>HAM-A</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1679,7 +1663,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HBI</t>
+          <t>HAMA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1689,46 +1673,46 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>C191036</t>
+          <t>C102118</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Harvey-Bradshaw Index Clinical Classification</t>
+          <t>Hamilton Anxiety Rating Scale Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HBI01</t>
+          <t>HAMA Questionnaire Question</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>exact_name</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>C191036</t>
+          <t>C101876</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Harvey-Bradshaw Index Clinical Classification</t>
+          <t>HAMA Questionnaire Question</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Hamilton Anxiety Rating Scale Clinical Classification</t>
+          <t>HAMA1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1745,12 +1729,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Harvey-Bradshaw Index Clinical Classification</t>
+          <t>HBI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1767,101 +1751,109 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
+          <t>HBI01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>C190943</t>
+          <t>C191036</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
+          <t>Harvey-Bradshaw Index Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IRANO 2015</t>
+          <t>Hamilton Anxiety Rating Scale Clinical Classification</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+          <t>exact_name</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>C102118</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Hamilton Anxiety Rating Scale Clinical Classification</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IWC HALLEK CLL 2018</t>
+          <t>Harvey-Bradshaw Index Clinical Classification</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+          <t>exact_name</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>C191036</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Harvey-Bradshaw Index Clinical Classification</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KFSS</t>
+          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>exact_name</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>C112522</t>
+          <t>C190943</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Kurtzke Functional Systems Scores Clinical Classification</t>
+          <t>Harvey-Bradshaw Index Clinical Classification Question</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>KFSS Questionnaire Question</t>
+          <t>IRANO 2015</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>exact_name</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>C112460</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>KFSS Questionnaire Question</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>KFSS1</t>
+          <t>IWC HALLEK CLL 2018</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1875,7 +1867,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>KPS SCALE</t>
+          <t>KFSS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1885,19 +1877,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>C100768</t>
+          <t>C112522</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Karnofsky Performance Status Scale Clinical Classification</t>
+          <t>Kurtzke Functional Systems Scores Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KPS Scale Questionnaire Question</t>
+          <t>KFSS Questionnaire Question</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1907,46 +1899,38 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>C100116</t>
+          <t>C112460</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KPS Scale Questionnaire Question</t>
+          <t>KFSS Questionnaire Question</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KPSS01</t>
+          <t>KFSS1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>synonym</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>C100768</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Karnofsky Performance Status Scale Clinical Classification</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Karnofsky Performance Status Scale Clinical Classification</t>
+          <t>KPS SCALE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1963,7 +1947,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kurtzke Functional Systems Scores Clinical Classification</t>
+          <t>KPS Scale Questionnaire Question</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1973,163 +1957,187 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>C112522</t>
+          <t>C100116</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Kurtzke Functional Systems Scores Clinical Classification</t>
+          <t>KPS Scale Questionnaire Question</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LUGANO CLASSIFICATION</t>
+          <t>KPSS01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+          <t>synonym</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>C100768</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Karnofsky Performance Status Scale Clinical Classification</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MVAI</t>
+          <t>Karnofsky Performance Status Scale Clinical Classification</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>exact_name</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>C191038</t>
+          <t>C100768</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Modified Van Assche Index Clinical Classification</t>
+          <t>Karnofsky Performance Status Scale Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MVAI1</t>
+          <t>Kurtzke Functional Systems Scores Clinical Classification</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>exact_name</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>C191038</t>
+          <t>C112522</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Modified Van Assche Index Clinical Classification</t>
+          <t>Kurtzke Functional Systems Scores Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Modified Van Assche Index Clinical Classification</t>
+          <t>LUGANO CLASSIFICATION</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>exact_name</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>C191038</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Modified Van Assche Index Clinical Classification</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Modified Van Assche Index Clinical Classification Question</t>
+          <t>MVAI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>C190945</t>
+          <t>C191038</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Modified Van Assche Index Clinical Classification Question</t>
+          <t>Modified Van Assche Index Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Oncology Standards</t>
+          <t>MVAI1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+          <t>synonym</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>C191038</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Modified Van Assche Index Clinical Classification</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PONTE-DI-LEGNO CONSORTIUM 2022</t>
+          <t>Modified Van Assche Index Clinical Classification</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
+          <t>exact_name</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>C191038</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Modified Van Assche Index Clinical Classification</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>QRS</t>
+          <t>Modified Van Assche Index Clinical Classification Question</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
+          <t>exact_name</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>C190945</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Modified Van Assche Index Clinical Classification Question</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>QRS Instrument Question</t>
+          <t>Oncology Standards</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2143,35 +2151,51 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Questionnaires</t>
+          <t>PASI FREDRIKSSON</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
+          <t>synonym</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>C191040</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RAJKUMAR MYELOMA 2011</t>
+          <t>PASI03</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
+          <t>synonym</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>C191040</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>RANO</t>
+          <t>PONTE-DI-LEGNO CONSORTIUM 2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2185,167 +2209,135 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>RECIST 1.1</t>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
+          <t>exact_name</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>C191040</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
+          <t>exact_name</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>C190947</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Psoriasis Area and Severity Index Fredriksson Version Clinical Classification Question</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>RUTG01</t>
+          <t>QRS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>synonym</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>C190946</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Rutgeerts Score Clinical Classification Question</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>RUTGEERTS SCORE</t>
+          <t>QRS Instrument Question</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>synonym</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>C190946</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Rutgeerts Score Clinical Classification Question</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Rutgeerts Score Clinical Classification</t>
+          <t>Questionnaires</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>exact_name</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>C191039</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Rutgeerts Score Clinical Classification</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Rutgeerts Score Clinical Classification Question</t>
+          <t>RAJKUMAR MYELOMA 2011</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>exact_name</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>C190946</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Rutgeerts Score Clinical Classification Question</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SIX MINUTE WALK</t>
+          <t>RANO</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>synonym</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>C115789</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>6 Minute Walk Functional Test 2008 Version</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SIXMW1</t>
+          <t>RECIST 1.1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>synonym</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>C115789</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>6 Minute Walk Functional Test 2008 Version</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Surveys</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2359,7 +2351,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TANN01</t>
+          <t>RUTG01</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2369,19 +2361,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>C124704</t>
+          <t>C190946</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tanner Scale Girl Version</t>
+          <t>Rutgeerts Score Clinical Classification Question</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TANN02</t>
+          <t>RUTGEERTS SCORE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2391,151 +2383,143 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>C124703</t>
+          <t>C190946</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tanner Scale Boy Version</t>
+          <t>Rutgeerts Score Clinical Classification Question</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TANNER SCALE BOY</t>
+          <t>Rutgeerts Score Clinical Classification</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>exact_name</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>C124703</t>
+          <t>C191039</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Tanner Scale Boy Version</t>
+          <t>Rutgeerts Score Clinical Classification</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TANNER SCALE GIRL</t>
+          <t>Rutgeerts Score Clinical Classification Question</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>exact_name</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>C124704</t>
+          <t>C190946</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tanner Scale Girl Version</t>
+          <t>Rutgeerts Score Clinical Classification Question</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Tanner Scale Boy Version</t>
+          <t>SIX MINUTE WALK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>C124703</t>
+          <t>C115789</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tanner Scale Boy Version</t>
+          <t>6 Minute Walk Functional Test 2008 Version</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tanner Scale Girl Version</t>
+          <t>SIXMW1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>C124704</t>
+          <t>C115789</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tanner Scale Girl Version</t>
+          <t>6 Minute Walk Functional Test 2008 Version</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Tanner Scale-Boy</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>synonym</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>C124703</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Tanner Scale Boy Version</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Tanner Scale-Boy Clinical Classification Question</t>
+          <t>TANN01</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>C124689</t>
+          <t>C124704</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Tanner Scale-Boy Clinical Classification Question</t>
+          <t>Tanner Scale Girl Version</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tanner Scale-Girl</t>
+          <t>TANN02</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2545,64 +2529,218 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>C124704</t>
+          <t>C124703</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tanner Scale Girl Version</t>
+          <t>Tanner Scale Boy Version</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Tanner Scale-Girl Clinical Classification Question</t>
+          <t>TANNER SCALE BOY</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>exact_name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>C124690</t>
+          <t>C124703</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Tanner Scale-Girl Clinical Classification Question</t>
+          <t>Tanner Scale Boy Version</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>iRANO</t>
+          <t>TANNER SCALE GIRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
+          <t>synonym</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>C124704</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Tanner Scale Girl Version</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>Tanner Scale Boy Version</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>exact_name</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>C124703</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Tanner Scale Boy Version</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Tanner Scale Girl Version</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>exact_name</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>C124704</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Tanner Scale Girl Version</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Tanner Scale-Boy</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>synonym</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>C124703</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Tanner Scale Boy Version</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Tanner Scale-Boy Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>exact_name</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>C124689</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Tanner Scale-Boy Clinical Classification Question</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Tanner Scale-Girl</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>synonym</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>C124704</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Tanner Scale Girl Version</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Tanner Scale-Girl Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>exact_name</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>C124690</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Tanner Scale-Girl Clinical Classification Question</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>iRANO</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>iRECIST</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2641,7 +2779,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -2651,7 +2789,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -2671,7 +2809,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
